--- a/docs/reservastest.xlsx
+++ b/docs/reservastest.xlsx
@@ -15,15 +15,19 @@
     <sheet sheetId="9" name="Menú Buffet+Aper+Vino" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="Menú Buffet+Aper+Vino+Bebida" state="visible" r:id="rId13"/>
     <sheet sheetId="11" name="Menú Buffet+Aper+Vino+Beb+Trago" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Accesibilidad" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="Tarifas" state="visible" r:id="rId16"/>
+    <sheet sheetId="12" name="Almuerzo" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Cena" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Con abono" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="Accesibilidad" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="Tarifas" state="visible" r:id="rId19"/>
+    <sheet sheetId="17" name="Horarios" state="visible" r:id="rId20"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="72">
   <si>
     <t>Encargado de la mesa</t>
   </si>
@@ -37,6 +41,9 @@
     <t>Hora</t>
   </si>
   <si>
+    <t>Servicio</t>
+  </si>
+  <si>
     <t>Adultos</t>
   </si>
   <si>
@@ -64,60 +71,105 @@
     <t>Total estimado (CLP)</t>
   </si>
   <si>
+    <t>Abono (CLP)</t>
+  </si>
+  <si>
+    <t>Saldo pendiente (CLP)</t>
+  </si>
+  <si>
     <t>Creada en</t>
   </si>
   <si>
+    <t>Camila Rojas</t>
+  </si>
+  <si>
+    <t>+56 9 8765 4321</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>Almuerzo</t>
+  </si>
+  <si>
+    <t>Buffet + Aperitivo + Vino + Bebida</t>
+  </si>
+  <si>
+    <t>Terraza Techada</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Aniversario de matrimonio</t>
+  </si>
+  <si>
+    <t>11-06-2026, 1:17:52 a. m.</t>
+  </si>
+  <si>
     <t>Pedro Soto</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>13:00</t>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>13:30</t>
   </si>
   <si>
     <t>Buffet</t>
   </si>
   <si>
-    <t>Sin preferencia</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>10-06-2026, 5:52:37 p. m.</t>
+    <t>Salón Eventos</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Almuerzo de empresa</t>
+  </si>
+  <si>
+    <t>11-06-2026, 1:17:32 a. m.</t>
   </si>
   <si>
     <t>María González</t>
   </si>
   <si>
-    <t>2026-07-15</t>
+    <t>+56 9 1234 5678</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
   </si>
   <si>
     <t>20:30</t>
   </si>
   <si>
+    <t>Cena</t>
+  </si>
+  <si>
     <t>Buffet + Aperitivo + Vino</t>
   </si>
   <si>
-    <t>Terraza Techada</t>
-  </si>
-  <si>
-    <t>Sí</t>
-  </si>
-  <si>
-    <t>Cumpleaños, torta a las 22:00</t>
+    <t>Salón 1</t>
+  </si>
+  <si>
+    <t>Cumpleaños, traemos torta</t>
+  </si>
+  <si>
+    <t>TOTAL (3 reservas)</t>
+  </si>
+  <si>
+    <t>TOTAL (1 reservas)</t>
   </si>
   <si>
     <t>TOTAL (2 reservas)</t>
   </si>
   <si>
-    <t>TOTAL (1 reservas)</t>
-  </si>
-  <si>
     <t>Concepto</t>
   </si>
   <si>
@@ -158,6 +210,39 @@
   </si>
   <si>
     <t>$4.990</t>
+  </si>
+  <si>
+    <t>Abono obligatorio para mesas de 10 o más personas</t>
+  </si>
+  <si>
+    <t>Se descuenta del total</t>
+  </si>
+  <si>
+    <t>Día</t>
+  </si>
+  <si>
+    <t>Almuerzo (ingreso)</t>
+  </si>
+  <si>
+    <t>Cena (ingreso)</t>
+  </si>
+  <si>
+    <t>Viernes</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>18:30 a 22:15</t>
+  </si>
+  <si>
+    <t>Sábado</t>
+  </si>
+  <si>
+    <t>12:45 a 16:15</t>
+  </si>
+  <si>
+    <t>Domingo</t>
   </si>
 </sst>
 </file>
@@ -554,25 +639,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -609,123 +697,209 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
         <v>2</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="1">
+        <v>241580</v>
+      </c>
+      <c r="O2" s="1">
+        <v>50000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>191580</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="1">
+        <v>235880</v>
+      </c>
+      <c r="O3" s="1">
+        <v>120000</v>
+      </c>
+      <c r="P3" s="1">
+        <v>115880</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1">
-        <v>41980</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" s="1">
+        <v>121980</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>121980</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="4">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3">
+      <c r="G5" s="4">
         <v>4</v>
       </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
+      <c r="H5" s="4">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="I5" s="4">
         <v>28</v>
       </c>
-      <c r="M3" s="1">
-        <v>126970</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="4">
-        <v>6</v>
-      </c>
-      <c r="F4" s="4">
-        <v>2</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4">
-        <v>9</v>
-      </c>
-      <c r="M4" s="5">
-        <v>168950</v>
+      <c r="N5" s="5">
+        <v>599440</v>
+      </c>
+      <c r="O5" s="5">
+        <v>170000</v>
+      </c>
+      <c r="P5" s="5">
+        <v>429440</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -733,25 +907,28 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -788,15 +965,103 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="1">
+        <v>241580</v>
+      </c>
+      <c r="O2" s="1">
+        <v>50000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>191580</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="4">
+        <v>8</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>10</v>
+      </c>
+      <c r="N3" s="5">
+        <v>241580</v>
+      </c>
+      <c r="O3" s="5">
+        <v>50000</v>
+      </c>
+      <c r="P3" s="5">
+        <v>191580</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -804,25 +1069,28 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -859,15 +1127,24 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -875,25 +1152,28 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -930,79 +1210,156 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="L2" t="s">
         <v>24</v>
       </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="1">
+        <v>241580</v>
+      </c>
+      <c r="O2" s="1">
+        <v>50000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>191580</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="1">
+        <v>235880</v>
+      </c>
+      <c r="O3" s="1">
+        <v>120000</v>
+      </c>
+      <c r="P3" s="1">
+        <v>115880</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="4">
+        <v>19</v>
+      </c>
+      <c r="G4" s="4">
         <v>2</v>
       </c>
-      <c r="G2">
+      <c r="H4" s="4">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>7</v>
-      </c>
-      <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="1">
-        <v>126970</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="4">
-        <v>4</v>
-      </c>
-      <c r="F3" s="4">
-        <v>2</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4">
-        <v>7</v>
-      </c>
-      <c r="M3" s="5">
-        <v>126970</v>
+      <c r="I4" s="4">
+        <v>22</v>
+      </c>
+      <c r="N4" s="5">
+        <v>477460</v>
+      </c>
+      <c r="O4" s="5">
+        <v>170000</v>
+      </c>
+      <c r="P4" s="5">
+        <v>307460</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1010,7 +1367,546 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>6</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="1">
+        <v>121980</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>121980</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="4">
+        <v>4</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>6</v>
+      </c>
+      <c r="N3" s="5">
+        <v>121980</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5">
+        <v>121980</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="1">
+        <v>241580</v>
+      </c>
+      <c r="O2" s="1">
+        <v>50000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>191580</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="1">
+        <v>235880</v>
+      </c>
+      <c r="O3" s="1">
+        <v>120000</v>
+      </c>
+      <c r="P3" s="1">
+        <v>115880</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="4">
+        <v>19</v>
+      </c>
+      <c r="G4" s="4">
+        <v>2</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4">
+        <v>22</v>
+      </c>
+      <c r="N4" s="5">
+        <v>477460</v>
+      </c>
+      <c r="O4" s="5">
+        <v>170000</v>
+      </c>
+      <c r="P4" s="5">
+        <v>307460</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="1">
+        <v>235880</v>
+      </c>
+      <c r="O2" s="1">
+        <v>120000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>115880</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="4">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4">
+        <v>12</v>
+      </c>
+      <c r="N3" s="5">
+        <v>235880</v>
+      </c>
+      <c r="O3" s="5">
+        <v>120000</v>
+      </c>
+      <c r="P3" s="5">
+        <v>115880</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -1019,58 +1915,125 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1081,25 +2044,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1136,15 +2102,103 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="1">
+        <v>235880</v>
+      </c>
+      <c r="O2" s="1">
+        <v>120000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>115880</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="4">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4">
+        <v>12</v>
+      </c>
+      <c r="N3" s="5">
+        <v>235880</v>
+      </c>
+      <c r="O3" s="5">
+        <v>120000</v>
+      </c>
+      <c r="P3" s="5">
+        <v>115880</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1152,25 +2206,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1207,15 +2264,103 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>6</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="1">
+        <v>121980</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>121980</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="4">
+        <v>4</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>6</v>
+      </c>
+      <c r="N3" s="5">
+        <v>121980</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5">
+        <v>121980</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1223,25 +2368,28 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1278,15 +2426,24 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1294,25 +2451,28 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1349,15 +2509,24 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1365,25 +2534,28 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1420,79 +2592,103 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="L2" t="s">
         <v>24</v>
       </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="1">
+        <v>241580</v>
+      </c>
+      <c r="O2" s="1">
+        <v>50000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>191580</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="4">
+        <v>8</v>
+      </c>
+      <c r="G3" s="4">
         <v>2</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>7</v>
-      </c>
-      <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="1">
-        <v>126970</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="4">
-        <v>4</v>
-      </c>
-      <c r="F3" s="4">
-        <v>2</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
       <c r="H3" s="4">
-        <v>7</v>
-      </c>
-      <c r="M3" s="5">
-        <v>126970</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>10</v>
+      </c>
+      <c r="N3" s="5">
+        <v>241580</v>
+      </c>
+      <c r="O3" s="5">
+        <v>50000</v>
+      </c>
+      <c r="P3" s="5">
+        <v>191580</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1500,25 +2696,28 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1555,79 +2754,24 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1">
-        <v>41980</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="4">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>41980</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1635,25 +2779,28 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1690,79 +2837,103 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1">
-        <v>41980</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="1">
+        <v>235880</v>
+      </c>
+      <c r="O2" s="1">
+        <v>120000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>115880</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="4">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F3" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>41980</v>
+        <v>1</v>
+      </c>
+      <c r="I3" s="4">
+        <v>12</v>
+      </c>
+      <c r="N3" s="5">
+        <v>235880</v>
+      </c>
+      <c r="O3" s="5">
+        <v>120000</v>
+      </c>
+      <c r="P3" s="5">
+        <v>115880</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1770,25 +2941,28 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="42" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="45" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="45" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1825,79 +2999,103 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>6</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" t="s">
         <v>24</v>
       </c>
-      <c r="E2">
+      <c r="M2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="1">
+        <v>121980</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>121980</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="4">
         <v>4</v>
       </c>
-      <c r="F2">
+      <c r="G3" s="4">
         <v>2</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>7</v>
-      </c>
-      <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="1">
-        <v>126970</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="4">
-        <v>4</v>
-      </c>
-      <c r="F3" s="4">
-        <v>2</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
       <c r="H3" s="4">
-        <v>7</v>
-      </c>
-      <c r="M3" s="5">
-        <v>126970</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>6</v>
+      </c>
+      <c r="N3" s="5">
+        <v>121980</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5">
+        <v>121980</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/reservastest.xlsx
+++ b/docs/reservastest.xlsx
@@ -19,19 +19,23 @@
     <sheet sheetId="13" name="Cena" state="visible" r:id="rId16"/>
     <sheet sheetId="14" name="Con abono" state="visible" r:id="rId17"/>
     <sheet sheetId="15" name="Accesibilidad" state="visible" r:id="rId18"/>
-    <sheet sheetId="16" name="Tarifas" state="visible" r:id="rId19"/>
-    <sheet sheetId="17" name="Horarios" state="visible" r:id="rId20"/>
+    <sheet sheetId="16" name="Canceladas" state="visible" r:id="rId19"/>
+    <sheet sheetId="17" name="Tarifas" state="visible" r:id="rId20"/>
+    <sheet sheetId="18" name="Horarios" state="visible" r:id="rId21"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="89">
   <si>
     <t>Encargado de la mesa</t>
   </si>
   <si>
+    <t>Correo</t>
+  </si>
+  <si>
     <t>Teléfono</t>
   </si>
   <si>
@@ -80,94 +84,142 @@
     <t>Creada en</t>
   </si>
   <si>
-    <t>Camila Rojas</t>
-  </si>
-  <si>
-    <t>+56 9 8765 4321</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
+    <t>Jorge Fuentes</t>
+  </si>
+  <si>
+    <t>jorge.fuentes@ejemplo.cl</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>Almuerzo</t>
+  </si>
+  <si>
+    <t>Buffet + Aperitivo + Vino</t>
+  </si>
+  <si>
+    <t>Sin preferencia</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Acceso para silla de ruedas</t>
+  </si>
+  <si>
+    <t>11-06-2026, 6:58:26 a. m.</t>
+  </si>
+  <si>
+    <t>Ana Riquelme</t>
+  </si>
+  <si>
+    <t>ana.riquelme@ejemplo.cl</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>Buffet</t>
+  </si>
+  <si>
+    <t>2do Piso</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Dos sillas para bebé</t>
+  </si>
+  <si>
+    <t>Empresa Andina Ltda.</t>
+  </si>
+  <si>
+    <t>eventos@andina.cl</t>
+  </si>
+  <si>
+    <t>+56 2 2345 6789</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>Cena</t>
+  </si>
+  <si>
+    <t>Buffet + Aperitivo + Vino + Bebida + Trago</t>
+  </si>
+  <si>
+    <t>Salón Eventos</t>
+  </si>
+  <si>
+    <t>Cena de empresa, factura a nombre de Andina Ltda.</t>
+  </si>
+  <si>
+    <t>Carlos Pérez</t>
+  </si>
+  <si>
+    <t>carlos.perez@ejemplo.cl</t>
   </si>
   <si>
     <t>13:00</t>
   </si>
   <si>
-    <t>Almuerzo</t>
-  </si>
-  <si>
-    <t>Buffet + Aperitivo + Vino + Bebida</t>
+    <t>Salón 1</t>
+  </si>
+  <si>
+    <t>María González</t>
+  </si>
+  <si>
+    <t>maria.gonzalez@ejemplo.cl</t>
+  </si>
+  <si>
+    <t>+56 9 1234 5678</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
   </si>
   <si>
     <t>Terraza Techada</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Aniversario de matrimonio</t>
-  </si>
-  <si>
-    <t>11-06-2026, 1:17:52 a. m.</t>
-  </si>
-  <si>
-    <t>Pedro Soto</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>Buffet</t>
-  </si>
-  <si>
-    <t>Salón Eventos</t>
-  </si>
-  <si>
-    <t>Sí</t>
-  </si>
-  <si>
-    <t>Almuerzo de empresa</t>
-  </si>
-  <si>
-    <t>11-06-2026, 1:17:32 a. m.</t>
-  </si>
-  <si>
-    <t>María González</t>
-  </si>
-  <si>
-    <t>+56 9 1234 5678</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>Cena</t>
-  </si>
-  <si>
-    <t>Buffet + Aperitivo + Vino</t>
-  </si>
-  <si>
-    <t>Salón 1</t>
-  </si>
-  <si>
-    <t>Cumpleaños, traemos torta</t>
+    <t>Cumpleaños, necesitamos torta a las 22:00</t>
+  </si>
+  <si>
+    <t>TOTAL (5 reservas)</t>
+  </si>
+  <si>
+    <t>TOTAL (1 reservas)</t>
+  </si>
+  <si>
+    <t>TOTAL (2 reservas)</t>
   </si>
   <si>
     <t>TOTAL (3 reservas)</t>
   </si>
   <si>
-    <t>TOTAL (1 reservas)</t>
-  </si>
-  <si>
-    <t>TOTAL (2 reservas)</t>
+    <t>Pamela Lagos</t>
+  </si>
+  <si>
+    <t>pamela.lagos@ejemplo.cl</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>Salón 2</t>
+  </si>
+  <si>
+    <t>Reserva de prueba que luego se cancela</t>
   </si>
   <si>
     <t>Concepto</t>
@@ -639,28 +691,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -700,7 +752,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -709,93 +761,99 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1">
+        <v>51000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>51000</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
         <v>10</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="1">
-        <v>241580</v>
-      </c>
-      <c r="O2" s="1">
-        <v>50000</v>
-      </c>
-      <c r="P2" s="1">
-        <v>191580</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
       </c>
       <c r="K3" t="s">
         <v>32</v>
@@ -806,20 +864,23 @@
       <c r="M3" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="1">
-        <v>235880</v>
+      <c r="N3" t="s">
+        <v>35</v>
       </c>
       <c r="O3" s="1">
-        <v>120000</v>
+        <v>144900</v>
       </c>
       <c r="P3" s="1">
-        <v>115880</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <v>20000</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>124900</v>
+      </c>
+      <c r="R3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -835,71 +896,186 @@
       <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="F4">
-        <v>4</v>
+      <c r="F4" t="s">
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>6</v>
-      </c>
-      <c r="J4" t="s">
-        <v>41</v>
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
       </c>
       <c r="K4" t="s">
         <v>42</v>
       </c>
       <c r="L4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="1">
+        <v>370800</v>
+      </c>
+      <c r="P4" s="1">
+        <v>150000</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>220800</v>
+      </c>
+      <c r="R4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="1">
+        <v>41980</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>41980</v>
+      </c>
+      <c r="R5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6" t="s">
         <v>24</v>
       </c>
-      <c r="M4" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4" s="1">
-        <v>121980</v>
-      </c>
-      <c r="O4" s="1">
-        <v>0</v>
-      </c>
-      <c r="P4" s="1">
-        <v>121980</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="4">
-        <v>23</v>
-      </c>
-      <c r="G5" s="4">
-        <v>4</v>
-      </c>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4">
+      <c r="L6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="1">
+        <v>126970</v>
+      </c>
+      <c r="P6" s="1">
+        <v>30000</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>96970</v>
+      </c>
+      <c r="R6" t="s">
         <v>28</v>
       </c>
-      <c r="N5" s="5">
-        <v>599440</v>
-      </c>
-      <c r="O5" s="5">
-        <v>170000</v>
-      </c>
-      <c r="P5" s="5">
-        <v>429440</v>
+    </row>
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="4">
+        <v>25</v>
+      </c>
+      <c r="H7" s="4">
+        <v>5</v>
+      </c>
+      <c r="I7" s="4">
+        <v>3</v>
+      </c>
+      <c r="J7" s="4">
+        <v>33</v>
+      </c>
+      <c r="O7" s="5">
+        <v>735650</v>
+      </c>
+      <c r="P7" s="5">
+        <v>200000</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>535650</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -907,28 +1083,28 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -968,7 +1144,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -977,91 +1153,15 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="1">
-        <v>241580</v>
-      </c>
-      <c r="O2" s="1">
-        <v>50000</v>
-      </c>
-      <c r="P2" s="1">
-        <v>191580</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="4">
-        <v>8</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>10</v>
-      </c>
-      <c r="N3" s="5">
-        <v>241580</v>
-      </c>
-      <c r="O3" s="5">
-        <v>50000</v>
-      </c>
-      <c r="P3" s="5">
-        <v>191580</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1069,28 +1169,28 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1130,7 +1230,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -1139,12 +1239,97 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2">
+        <v>12</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1">
+        <v>370800</v>
+      </c>
+      <c r="P2" s="1">
+        <v>150000</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>220800</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="4">
+        <v>12</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>12</v>
+      </c>
+      <c r="O3" s="5">
+        <v>370800</v>
+      </c>
+      <c r="P3" s="5">
+        <v>150000</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>220800</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1152,28 +1337,28 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1213,7 +1398,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -1222,93 +1407,99 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1">
+        <v>51000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>51000</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
         <v>10</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="1">
-        <v>241580</v>
-      </c>
-      <c r="O2" s="1">
-        <v>50000</v>
-      </c>
-      <c r="P2" s="1">
-        <v>191580</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
       </c>
       <c r="K3" t="s">
         <v>32</v>
@@ -1319,47 +1510,106 @@
       <c r="M3" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="1">
-        <v>235880</v>
+      <c r="N3" t="s">
+        <v>35</v>
       </c>
       <c r="O3" s="1">
-        <v>120000</v>
+        <v>144900</v>
       </c>
       <c r="P3" s="1">
-        <v>115880</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+        <v>20000</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>124900</v>
+      </c>
+      <c r="R3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="4">
-        <v>19</v>
-      </c>
-      <c r="G4" s="4">
-        <v>2</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4">
-        <v>22</v>
-      </c>
-      <c r="N4" s="5">
-        <v>477460</v>
-      </c>
-      <c r="O4" s="5">
-        <v>170000</v>
-      </c>
-      <c r="P4" s="5">
-        <v>307460</v>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="1">
+        <v>41980</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>41980</v>
+      </c>
+      <c r="R4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="4">
+        <v>9</v>
+      </c>
+      <c r="H5" s="4">
+        <v>3</v>
+      </c>
+      <c r="I5" s="4">
+        <v>2</v>
+      </c>
+      <c r="J5" s="4">
+        <v>14</v>
+      </c>
+      <c r="O5" s="5">
+        <v>237880</v>
+      </c>
+      <c r="P5" s="5">
+        <v>20000</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>217880</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1367,28 +1617,28 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1428,7 +1678,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -1437,11 +1687,14 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -1457,71 +1710,130 @@
       <c r="E2" t="s">
         <v>40</v>
       </c>
-      <c r="F2">
-        <v>4</v>
+      <c r="F2" t="s">
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2" t="s">
-        <v>41</v>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>12</v>
       </c>
       <c r="K2" t="s">
         <v>42</v>
       </c>
       <c r="L2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1">
+        <v>370800</v>
+      </c>
+      <c r="P2" s="1">
+        <v>150000</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>220800</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3" t="s">
         <v>24</v>
       </c>
-      <c r="M2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" s="1">
-        <v>121980</v>
-      </c>
-      <c r="O2" s="1">
-        <v>0</v>
-      </c>
-      <c r="P2" s="1">
-        <v>121980</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="4">
-        <v>4</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>6</v>
-      </c>
-      <c r="N3" s="5">
-        <v>121980</v>
-      </c>
-      <c r="O3" s="5">
-        <v>0</v>
-      </c>
-      <c r="P3" s="5">
-        <v>121980</v>
+      <c r="L3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="1">
+        <v>126970</v>
+      </c>
+      <c r="P3" s="1">
+        <v>30000</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>96970</v>
+      </c>
+      <c r="R3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="4">
+        <v>16</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4">
+        <v>19</v>
+      </c>
+      <c r="O4" s="5">
+        <v>497770</v>
+      </c>
+      <c r="P4" s="5">
+        <v>180000</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>317770</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1529,28 +1841,28 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1590,7 +1902,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -1599,144 +1911,209 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
         <v>10</v>
       </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="1">
-        <v>241580</v>
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>35</v>
       </c>
       <c r="O2" s="1">
-        <v>50000</v>
+        <v>144900</v>
       </c>
       <c r="P2" s="1">
-        <v>191580</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>20000</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>124900</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>12</v>
       </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="1">
-        <v>235880</v>
+      <c r="N3" t="s">
+        <v>44</v>
       </c>
       <c r="O3" s="1">
-        <v>120000</v>
+        <v>370800</v>
       </c>
       <c r="P3" s="1">
-        <v>115880</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="4">
-        <v>19</v>
-      </c>
-      <c r="G4" s="4">
-        <v>2</v>
-      </c>
-      <c r="H4" s="4">
+        <v>150000</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>220800</v>
+      </c>
+      <c r="R3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
-      <c r="I4" s="4">
-        <v>22</v>
-      </c>
-      <c r="N4" s="5">
-        <v>477460</v>
-      </c>
-      <c r="O4" s="5">
-        <v>170000</v>
-      </c>
-      <c r="P4" s="5">
-        <v>307460</v>
+      <c r="J4">
+        <v>7</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" s="1">
+        <v>126970</v>
+      </c>
+      <c r="P4" s="1">
+        <v>30000</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>96970</v>
+      </c>
+      <c r="R4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="4">
+        <v>21</v>
+      </c>
+      <c r="H5" s="4">
+        <v>5</v>
+      </c>
+      <c r="I5" s="4">
+        <v>3</v>
+      </c>
+      <c r="J5" s="4">
+        <v>29</v>
+      </c>
+      <c r="O5" s="5">
+        <v>642670</v>
+      </c>
+      <c r="P5" s="5">
+        <v>200000</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>442670</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1744,28 +2121,28 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1805,7 +2182,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -1814,97 +2191,327 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
+      <c r="O2" s="1">
+        <v>51000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>51000</v>
+      </c>
+      <c r="R2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" s="1">
-        <v>235880</v>
-      </c>
-      <c r="O2" s="1">
-        <v>120000</v>
-      </c>
-      <c r="P2" s="1">
-        <v>115880</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="4">
-        <v>11</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="1">
+        <v>126970</v>
+      </c>
+      <c r="P3" s="1">
+        <v>30000</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>96970</v>
+      </c>
+      <c r="R3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="4">
+        <v>6</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4">
         <v>1</v>
       </c>
-      <c r="I3" s="4">
-        <v>12</v>
-      </c>
-      <c r="N3" s="5">
-        <v>235880</v>
-      </c>
-      <c r="O3" s="5">
-        <v>120000</v>
-      </c>
-      <c r="P3" s="5">
-        <v>115880</v>
+      <c r="J4" s="4">
+        <v>9</v>
+      </c>
+      <c r="O4" s="5">
+        <v>177970</v>
+      </c>
+      <c r="P4" s="5">
+        <v>30000</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>147970</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2">
+        <v>6</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O2" s="1">
+        <v>135930</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>135930</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="4">
+        <v>6</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>7</v>
+      </c>
+      <c r="O3" s="5">
+        <v>135930</v>
+      </c>
+      <c r="P3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>135930</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1915,66 +2522,66 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1983,7 +2590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1994,46 +2601,46 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2044,28 +2651,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2105,7 +2712,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -2114,91 +2721,97 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>11</v>
+        <v>40</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="1">
-        <v>235880</v>
+      <c r="N2" t="s">
+        <v>44</v>
       </c>
       <c r="O2" s="1">
-        <v>120000</v>
+        <v>370800</v>
       </c>
       <c r="P2" s="1">
-        <v>115880</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>150000</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>220800</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="4">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="G3" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H3" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
         <v>12</v>
       </c>
-      <c r="N3" s="5">
-        <v>235880</v>
-      </c>
       <c r="O3" s="5">
-        <v>120000</v>
+        <v>370800</v>
       </c>
       <c r="P3" s="5">
-        <v>115880</v>
+        <v>150000</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>220800</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2206,28 +2819,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2267,7 +2880,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -2276,28 +2889,31 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
         <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -2306,39 +2922,39 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>6</v>
-      </c>
-      <c r="J2" t="s">
-        <v>41</v>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="M2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" s="1">
-        <v>121980</v>
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
       </c>
       <c r="O2" s="1">
-        <v>0</v>
+        <v>41980</v>
       </c>
       <c r="P2" s="1">
-        <v>121980</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>41980</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="4">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="G3" s="4">
         <v>2</v>
@@ -2347,20 +2963,23 @@
         <v>0</v>
       </c>
       <c r="I3" s="4">
-        <v>6</v>
-      </c>
-      <c r="N3" s="5">
-        <v>121980</v>
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>2</v>
       </c>
       <c r="O3" s="5">
-        <v>0</v>
+        <v>41980</v>
       </c>
       <c r="P3" s="5">
-        <v>121980</v>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>41980</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2368,28 +2987,28 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2429,7 +3048,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -2438,12 +3057,15 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2451,28 +3073,28 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2512,7 +3134,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -2521,12 +3143,97 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>10</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" s="1">
+        <v>144900</v>
+      </c>
+      <c r="P2" s="1">
+        <v>20000</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>124900</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="4">
+        <v>5</v>
+      </c>
+      <c r="H3" s="4">
+        <v>3</v>
+      </c>
+      <c r="I3" s="4">
+        <v>2</v>
+      </c>
+      <c r="J3" s="4">
+        <v>10</v>
+      </c>
+      <c r="O3" s="5">
+        <v>144900</v>
+      </c>
+      <c r="P3" s="5">
+        <v>20000</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>124900</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2534,28 +3241,28 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2595,7 +3302,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -2604,91 +3311,97 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
+        <v>40</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="1">
-        <v>241580</v>
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>54</v>
       </c>
       <c r="O2" s="1">
-        <v>50000</v>
+        <v>126970</v>
       </c>
       <c r="P2" s="1">
-        <v>191580</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>30000</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>96970</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="4">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="G3" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>10</v>
-      </c>
-      <c r="N3" s="5">
-        <v>241580</v>
+        <v>1</v>
+      </c>
+      <c r="J3" s="4">
+        <v>7</v>
       </c>
       <c r="O3" s="5">
-        <v>50000</v>
+        <v>126970</v>
       </c>
       <c r="P3" s="5">
-        <v>191580</v>
+        <v>30000</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>96970</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2696,28 +3409,28 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2757,7 +3470,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -2766,12 +3479,97 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1">
+        <v>51000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>51000</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>2</v>
+      </c>
+      <c r="O3" s="5">
+        <v>51000</v>
+      </c>
+      <c r="P3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>51000</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2779,28 +3577,28 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2840,7 +3638,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -2849,40 +3647,43 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>11</v>
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>10</v>
       </c>
       <c r="K2" t="s">
         <v>32</v>
@@ -2893,47 +3694,106 @@
       <c r="M2" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="1">
-        <v>235880</v>
+      <c r="N2" t="s">
+        <v>35</v>
       </c>
       <c r="O2" s="1">
-        <v>120000</v>
+        <v>144900</v>
       </c>
       <c r="P2" s="1">
-        <v>115880</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+        <v>20000</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>124900</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="4">
-        <v>11</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4">
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="1">
+        <v>41980</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>41980</v>
+      </c>
+      <c r="R3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="4">
+        <v>7</v>
+      </c>
+      <c r="H4" s="4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="4">
+        <v>2</v>
+      </c>
+      <c r="J4" s="4">
         <v>12</v>
       </c>
-      <c r="N3" s="5">
-        <v>235880</v>
-      </c>
-      <c r="O3" s="5">
-        <v>120000</v>
-      </c>
-      <c r="P3" s="5">
-        <v>115880</v>
+      <c r="O4" s="5">
+        <v>186880</v>
+      </c>
+      <c r="P4" s="5">
+        <v>20000</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>166880</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2941,28 +3801,28 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="45" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3002,7 +3862,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -3011,91 +3871,153 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1">
+        <v>51000</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>51000</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
         <v>40</v>
       </c>
-      <c r="F2">
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3">
         <v>4</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="1">
+        <v>126970</v>
+      </c>
+      <c r="P3" s="1">
+        <v>30000</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>96970</v>
+      </c>
+      <c r="R3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="4">
         <v>6</v>
       </c>
-      <c r="J2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" s="1">
-        <v>121980</v>
-      </c>
-      <c r="O2" s="1">
-        <v>0</v>
-      </c>
-      <c r="P2" s="1">
-        <v>121980</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="4">
-        <v>4</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>6</v>
-      </c>
-      <c r="N3" s="5">
-        <v>121980</v>
-      </c>
-      <c r="O3" s="5">
-        <v>0</v>
-      </c>
-      <c r="P3" s="5">
-        <v>121980</v>
+      <c r="H4" s="4">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4">
+        <v>9</v>
+      </c>
+      <c r="O4" s="5">
+        <v>177970</v>
+      </c>
+      <c r="P4" s="5">
+        <v>30000</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>147970</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
